--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -885,15 +885,15 @@
         <v>21</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-93.333333333333</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>9</v>
@@ -926,7 +926,7 @@
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E16" s="15">
+        <v>22.222222222222</v>
+      </c>
+      <c r="F16" s="14">
+        <v>33</v>
+      </c>
+      <c r="G16" s="14">
+        <v>33</v>
+      </c>
+      <c r="H16" s="15">
         <v>0</v>
       </c>
-      <c r="F16" s="14">
-        <v>32</v>
-      </c>
-      <c r="G16" s="14">
-        <v>31</v>
-      </c>
-      <c r="H16" s="15">
-        <v>3.225806451612</v>
-      </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="J16" s="14">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K16" s="15">
-        <v>-2.127659574468</v>
+        <v>1.785714285714</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.984126984127</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-14.814814814814</v>
+        <v>0</v>
       </c>
       <c r="N16" s="15">
-        <v>-76.649746192893</v>
+        <v>-75.217391304347</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>14</v>
+      </c>
+      <c r="D17" s="14">
         <v>18</v>
       </c>
-      <c r="D17" s="14">
-        <v>16</v>
-      </c>
       <c r="E17" s="15">
-        <v>12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F17" s="14">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G17" s="14">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" s="15">
-        <v>2.531645569620</v>
+        <v>-5</v>
       </c>
       <c r="I17" s="14">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="J17" s="14">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="K17" s="15">
-        <v>13.333333333333</v>
+        <v>11.382113821138</v>
       </c>
       <c r="L17" s="15">
-        <v>25.263157894736</v>
+        <v>19.130434782608</v>
       </c>
       <c r="M17" s="15">
-        <v>190.243902439024</v>
+        <v>191.489361702128</v>
       </c>
       <c r="N17" s="15">
-        <v>48.75</v>
+        <v>52.222222222222</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-57.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H18" s="15">
-        <v>-40</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="I18" s="14">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.581395348837</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L18" s="15">
-        <v>6.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>18.518518518518</v>
+        <v>37.931034482758</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.807947019867</v>
+        <v>-76.878612716763</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14">
         <v>13</v>
       </c>
-      <c r="D19" s="14">
-        <v>16</v>
-      </c>
       <c r="E19" s="15">
-        <v>-18.75</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G19" s="14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>-2.777777777777</v>
+        <v>-7.352941176470</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>2.173913043478</v>
+        <v>1.904761904761</v>
       </c>
       <c r="L19" s="15">
-        <v>-6</v>
+        <v>-3.603603603603</v>
       </c>
       <c r="M19" s="15">
-        <v>141.025641025641</v>
+        <v>160.975609756098</v>
       </c>
       <c r="N19" s="15">
-        <v>51.612903225806</v>
+        <v>40.789473684210</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>4</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>35.294117647058</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L20" s="15">
-        <v>27.777777777777</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>130</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N20" s="15">
-        <v>-67.142857142857</v>
+        <v>-69.879518072289</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.272727272727</v>
+        <v>-11.320754716981</v>
       </c>
       <c r="F21" s="17">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="G21" s="17">
         <v>229</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.183406113537</v>
+        <v>-8.296943231441</v>
       </c>
       <c r="I21" s="17">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="J21" s="17">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="K21" s="18">
-        <v>3.846153846153</v>
+        <v>3.013698630136</v>
       </c>
       <c r="L21" s="18">
-        <v>3.846153846153</v>
+        <v>1.347708894878</v>
       </c>
       <c r="M21" s="18">
-        <v>86.206896551724</v>
+        <v>96.858638743455</v>
       </c>
       <c r="N21" s="18">
-        <v>-43.75</v>
+        <v>-44.296296296296</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,34 +1183,34 @@
         <v>2</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F22" s="14">
+        <v>9</v>
+      </c>
+      <c r="G22" s="14">
         <v>8</v>
       </c>
-      <c r="G22" s="14">
-        <v>7</v>
-      </c>
       <c r="H22" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L22" s="15">
-        <v>-42.857142857142</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M22" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E23" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="F23" s="14">
+        <v>41</v>
+      </c>
+      <c r="G23" s="14">
+        <v>41</v>
+      </c>
+      <c r="H23" s="15">
         <v>0</v>
       </c>
-      <c r="F23" s="14">
-        <v>36</v>
-      </c>
-      <c r="G23" s="14">
-        <v>40</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-10</v>
-      </c>
       <c r="I23" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="J23" s="14">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.280701754386</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L23" s="15">
-        <v>-1.960784313725</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
-        <v>61.290322580645</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>23</v>
+      </c>
+      <c r="D24" s="14">
+        <v>22</v>
+      </c>
+      <c r="E24" s="15">
+        <v>4.545454545454</v>
+      </c>
+      <c r="F24" s="14">
+        <v>106</v>
+      </c>
+      <c r="G24" s="14">
+        <v>128</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-17.1875</v>
+      </c>
+      <c r="I24" s="14">
+        <v>190</v>
+      </c>
+      <c r="J24" s="14">
+        <v>206</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-7.766990291262</v>
+      </c>
+      <c r="L24" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="M24" s="15">
         <v>25</v>
-      </c>
-      <c r="D24" s="14">
-        <v>25</v>
-      </c>
-      <c r="E24" s="15">
-        <v>0</v>
-      </c>
-      <c r="F24" s="14">
-        <v>120</v>
-      </c>
-      <c r="G24" s="14">
-        <v>136</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-11.764705882352</v>
-      </c>
-      <c r="I24" s="14">
-        <v>163</v>
-      </c>
-      <c r="J24" s="14">
-        <v>184</v>
-      </c>
-      <c r="K24" s="15">
-        <v>-11.413043478260</v>
-      </c>
-      <c r="L24" s="15">
-        <v>-15.104166666666</v>
-      </c>
-      <c r="M24" s="15">
-        <v>19.852941176470</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>12.5</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H25" s="15">
-        <v>-40.625</v>
+        <v>-38.983050847457</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="J25" s="14">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="K25" s="15">
-        <v>-27.848101265822</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="L25" s="15">
-        <v>-37.362637362637</v>
+        <v>-39.823008849557</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D26" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="15">
-        <v>-36.666666666666</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F26" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.510638297872</v>
+        <v>-8.080808080808</v>
       </c>
       <c r="I26" s="14">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="J26" s="14">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.032258064516</v>
+        <v>-2</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.461538461538</v>
+        <v>-6.962025316455</v>
       </c>
       <c r="M26" s="15">
-        <v>17.821782178217</v>
+        <v>27.826086956521</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1397,22 +1397,22 @@
         <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>83.333333333333</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-42.857142857142</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1467,7 +1467,7 @@
         <v>36</v>
       </c>
       <c r="C29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1478,29 +1478,29 @@
       <c r="F29" s="14">
         <v>4</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>300</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J29" s="14">
         <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M29" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-81.481481481481</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1508,7 +1508,7 @@
         <v>37</v>
       </c>
       <c r="C30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1519,29 +1519,29 @@
       <c r="F30" s="14">
         <v>4</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>300</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-78.947368421052</v>
+        <v>-76.190476190476</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -881,11 +881,11 @@
       <c r="L14" s="15">
         <v>-50</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-93.333333333333</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>12.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>22.222222222222</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G16" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
         <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="J16" s="14">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K16" s="15">
-        <v>1.785714285714</v>
+        <v>1.612903225806</v>
       </c>
       <c r="L16" s="15">
-        <v>-25</v>
+        <v>-26.744186046511</v>
       </c>
       <c r="M16" s="15">
         <v>0</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.217391304347</v>
+        <v>-75.769230769230</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G17" s="14">
         <v>80</v>
       </c>
       <c r="H17" s="15">
-        <v>-5</v>
+        <v>-10</v>
       </c>
       <c r="I17" s="14">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="J17" s="14">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="K17" s="15">
-        <v>11.382113821138</v>
+        <v>10.144927536231</v>
       </c>
       <c r="L17" s="15">
-        <v>19.130434782608</v>
+        <v>16.030534351145</v>
       </c>
       <c r="M17" s="15">
-        <v>191.489361702128</v>
+        <v>162.068965517241</v>
       </c>
       <c r="N17" s="15">
-        <v>52.222222222222</v>
+        <v>50.495049504950</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="15">
-        <v>-11.111111111111</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H18" s="15">
-        <v>-38.235294117647</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J18" s="14">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.076923076923</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>14.285714285714</v>
+        <v>2.127659574468</v>
       </c>
       <c r="M18" s="15">
-        <v>37.931034482758</v>
+        <v>60</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.878612716763</v>
+        <v>-75.634517766497</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.692307692307</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.352941176470</v>
+        <v>-10.958904109589</v>
       </c>
       <c r="I19" s="14">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="K19" s="15">
-        <v>1.904761904761</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.603603603603</v>
+        <v>-3.076923076923</v>
       </c>
       <c r="M19" s="15">
-        <v>160.975609756098</v>
+        <v>152</v>
       </c>
       <c r="N19" s="15">
-        <v>40.789473684210</v>
+        <v>48.235294117647</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>19.047619047619</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.714285714285</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="M20" s="15">
-        <v>78.571428571428</v>
+        <v>87.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-69.879518072289</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D21" s="17">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>-11.320754716981</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="F21" s="17">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="G21" s="17">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.296943231441</v>
+        <v>-14.225941422594</v>
       </c>
       <c r="I21" s="17">
-        <v>376</v>
+        <v>430</v>
       </c>
       <c r="J21" s="17">
-        <v>365</v>
+        <v>427</v>
       </c>
       <c r="K21" s="18">
-        <v>3.013698630136</v>
+        <v>0.702576112412</v>
       </c>
       <c r="L21" s="18">
-        <v>1.347708894878</v>
+        <v>-0.462962962962</v>
       </c>
       <c r="M21" s="18">
-        <v>96.858638743455</v>
+        <v>94.570135746606</v>
       </c>
       <c r="N21" s="18">
-        <v>-44.296296296296</v>
+        <v>-43.346508563899</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
         <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>12.5</v>
+        <v>-25</v>
       </c>
       <c r="I22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="15">
-        <v>-11.111111111111</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G23" s="14">
         <v>41</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="I23" s="14">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K23" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="L23" s="15">
-        <v>0</v>
+        <v>3.076923076923</v>
       </c>
       <c r="M23" s="15">
-        <v>71.428571428571</v>
+        <v>76.315789473684</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>4.545454545454</v>
+        <v>80.769230769230</v>
       </c>
       <c r="F24" s="14">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="H24" s="15">
-        <v>-17.1875</v>
+        <v>16.513761467889</v>
       </c>
       <c r="I24" s="14">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="J24" s="14">
-        <v>206</v>
+        <v>232</v>
       </c>
       <c r="K24" s="15">
-        <v>-7.766990291262</v>
+        <v>2.155172413793</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.666666666666</v>
+        <v>-9.195402298850</v>
       </c>
       <c r="M24" s="15">
-        <v>25</v>
+        <v>42.771084337349</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.983050847457</v>
+        <v>-8</v>
       </c>
       <c r="I25" s="14">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="J25" s="14">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K25" s="15">
-        <v>-20.930232558139</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="L25" s="15">
-        <v>-39.823008849557</v>
+        <v>-28.925619834710</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>15.384615384615</v>
+        <v>8.695652173913</v>
       </c>
       <c r="F26" s="14">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G26" s="14">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="H26" s="15">
-        <v>-8.080808080808</v>
+        <v>3.191489361702</v>
       </c>
       <c r="I26" s="14">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="J26" s="14">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="K26" s="15">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.962025316455</v>
+        <v>-5.464480874316</v>
       </c>
       <c r="M26" s="15">
-        <v>27.826086956521</v>
+        <v>27.205882352941</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
+        <v>71.428571428571</v>
+      </c>
+      <c r="L27" s="15">
         <v>100</v>
-      </c>
-      <c r="L27" s="15">
-        <v>140</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>38.461538461538</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>38.461538461538</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>0</v>
       </c>
       <c r="F29" s="14">
+        <v>5</v>
+      </c>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>400</v>
+      </c>
+      <c r="I29" s="14">
+        <v>6</v>
+      </c>
+      <c r="J29" s="14">
         <v>4</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="14">
-        <v>5</v>
-      </c>
-      <c r="J29" s="14">
-        <v>3</v>
-      </c>
       <c r="K29" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M29" s="15">
-        <v>-37.5</v>
+        <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.481481481481</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>0</v>
       </c>
       <c r="F30" s="14">
+        <v>5</v>
+      </c>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>400</v>
+      </c>
+      <c r="I30" s="14">
+        <v>6</v>
+      </c>
+      <c r="J30" s="14">
         <v>4</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="14">
-        <v>5</v>
-      </c>
-      <c r="J30" s="14">
-        <v>3</v>
-      </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
-        <v>66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="M30" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.190476190476</v>
+        <v>-76.923076923076</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>100</v>
@@ -926,7 +926,7 @@
         <v>233.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>25</v>
+        <v>11.111111111111</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F16" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J16" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="K16" s="15">
-        <v>1.612903225806</v>
+        <v>7.246376811594</v>
       </c>
       <c r="L16" s="15">
-        <v>-26.744186046511</v>
+        <v>-22.105263157894</v>
       </c>
       <c r="M16" s="15">
-        <v>0</v>
+        <v>10.447761194029</v>
       </c>
       <c r="N16" s="15">
-        <v>-75.769230769230</v>
+        <v>-74.829931972789</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F17" s="14">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G17" s="14">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="H17" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
+        <v>168</v>
+      </c>
+      <c r="J17" s="14">
         <v>152</v>
       </c>
-      <c r="J17" s="14">
-        <v>138</v>
-      </c>
       <c r="K17" s="15">
-        <v>10.144927536231</v>
+        <v>10.526315789473</v>
       </c>
       <c r="L17" s="15">
-        <v>16.030534351145</v>
+        <v>13.513513513513</v>
       </c>
       <c r="M17" s="15">
-        <v>162.068965517241</v>
+        <v>170.967741935484</v>
       </c>
       <c r="N17" s="15">
-        <v>50.495049504950</v>
+        <v>41.176470588235</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>7</v>
       </c>
-      <c r="D18" s="14">
-        <v>12</v>
-      </c>
       <c r="E18" s="15">
-        <v>-41.666666666666</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F18" s="14">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H18" s="15">
-        <v>-39.473684210526</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-30.985915492957</v>
       </c>
       <c r="L18" s="15">
-        <v>2.127659574468</v>
+        <v>-18.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>60</v>
+        <v>48.484848484848</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.634517766497</v>
+        <v>-77.522935779816</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F19" s="14">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H19" s="15">
-        <v>-10.958904109589</v>
+        <v>-11.594202898550</v>
       </c>
       <c r="I19" s="14">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-2.068965517241</v>
       </c>
       <c r="L19" s="15">
-        <v>-3.076923076923</v>
+        <v>-5.960264900662</v>
       </c>
       <c r="M19" s="15">
-        <v>152</v>
+        <v>136.666666666667</v>
       </c>
       <c r="N19" s="15">
-        <v>48.235294117647</v>
+        <v>54.347826086956</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>7.142857142857</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.225806451612</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>87.5</v>
+        <v>72.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-66.666666666666</v>
+        <v>-68.686868686868</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>42</v>
+      </c>
+      <c r="D21" s="17">
         <v>48</v>
       </c>
-      <c r="D21" s="17">
-        <v>62</v>
-      </c>
       <c r="E21" s="18">
-        <v>-22.580645161290</v>
+        <v>-12.5</v>
       </c>
       <c r="F21" s="17">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="G21" s="17">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.225941422594</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="I21" s="17">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="J21" s="17">
-        <v>427</v>
+        <v>475</v>
       </c>
       <c r="K21" s="18">
-        <v>0.702576112412</v>
+        <v>0</v>
       </c>
       <c r="L21" s="18">
-        <v>-0.462962962962</v>
+        <v>-4.233870967741</v>
       </c>
       <c r="M21" s="18">
-        <v>94.570135746606</v>
+        <v>94.672131147541</v>
       </c>
       <c r="N21" s="18">
-        <v>-43.346508563899</v>
+        <v>-44.051825677267</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
+        <v>100</v>
+      </c>
+      <c r="F22" s="14">
+        <v>7</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="15">
         <v>0</v>
       </c>
-      <c r="F22" s="14">
-        <v>6</v>
-      </c>
-      <c r="G22" s="14">
-        <v>8</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-25</v>
-      </c>
       <c r="I22" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J22" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>-8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-38.888888888888</v>
+        <v>-35</v>
       </c>
       <c r="M22" s="15">
-        <v>120</v>
+        <v>62.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
         <v>6</v>
       </c>
-      <c r="D23" s="14">
-        <v>10</v>
-      </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G23" s="14">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>-7.317073170731</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="I23" s="14">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J23" s="14">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K23" s="15">
-        <v>-11.842105263157</v>
+        <v>-10.975609756097</v>
       </c>
       <c r="L23" s="15">
-        <v>3.076923076923</v>
+        <v>-2.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>76.315789473684</v>
+        <v>62.222222222222</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E24" s="15">
-        <v>80.769230769230</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="14">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H24" s="15">
-        <v>16.513761467889</v>
+        <v>7.317073170731</v>
       </c>
       <c r="I24" s="14">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="J24" s="14">
-        <v>232</v>
+        <v>282</v>
       </c>
       <c r="K24" s="15">
-        <v>2.155172413793</v>
+        <v>-3.900709219858</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.195402298850</v>
+        <v>-5.902777777777</v>
       </c>
       <c r="M24" s="15">
-        <v>42.771084337349</v>
+        <v>42.631578947368</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15">
-        <v>-8</v>
+        <v>19.148936170212</v>
       </c>
       <c r="I25" s="14">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="J25" s="14">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.307692307692</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="L25" s="15">
-        <v>-28.925619834710</v>
+        <v>-20</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>25</v>
       </c>
       <c r="D26" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>8.695652173913</v>
+        <v>19.047619047619</v>
       </c>
       <c r="F26" s="14">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="15">
-        <v>3.191489361702</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="J26" s="14">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>1.030927835051</v>
       </c>
       <c r="L26" s="15">
-        <v>-5.464480874316</v>
+        <v>-3.921568627450</v>
       </c>
       <c r="M26" s="15">
-        <v>27.205882352941</v>
+        <v>29.801324503311</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
+        <v>50</v>
+      </c>
+      <c r="L27" s="15">
         <v>71.428571428571</v>
-      </c>
-      <c r="L27" s="15">
-        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>9</v>
+      </c>
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="G28" s="14">
-        <v>9</v>
-      </c>
       <c r="H28" s="15">
-        <v>-22.222222222222</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L28" s="15">
-        <v>42.857142857142</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,90 +1466,90 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L29" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M29" s="15">
         <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I30" s="14">
         <v>6</v>
       </c>
       <c r="J30" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="L30" s="15">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="M30" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-76.923076923076</v>
+        <v>-79.310344827586</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>0</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
-      <c r="J33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="13" t="s">
-        <v>21</v>
+      <c r="J33" s="14">
+        <v>1</v>
+      </c>
+      <c r="K33" s="15">
+        <v>0</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,32 +854,32 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
       </c>
       <c r="J14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M14" s="15">
         <v>0</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,16 +899,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>10</v>
@@ -926,7 +926,7 @@
         <v>233.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>11.111111111111</v>
+        <v>-9.090909090909</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>57.142857142857</v>
+        <v>-10</v>
       </c>
       <c r="F16" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G16" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H16" s="15">
-        <v>22.222222222222</v>
+        <v>15.625</v>
       </c>
       <c r="I16" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J16" s="14">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K16" s="15">
-        <v>7.246376811594</v>
+        <v>5.063291139240</v>
       </c>
       <c r="L16" s="15">
-        <v>-22.105263157894</v>
+        <v>-20.952380952381</v>
       </c>
       <c r="M16" s="15">
-        <v>10.447761194029</v>
+        <v>16.901408450704</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.829931972789</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>7.142857142857</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F17" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="14">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H17" s="15">
         <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="J17" s="14">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="K17" s="15">
-        <v>10.526315789473</v>
+        <v>13.609467455621</v>
       </c>
       <c r="L17" s="15">
-        <v>13.513513513513</v>
+        <v>17.791411042944</v>
       </c>
       <c r="M17" s="15">
-        <v>170.967741935484</v>
+        <v>170.422535211268</v>
       </c>
       <c r="N17" s="15">
-        <v>41.176470588235</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>-85.714285714285</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G18" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I18" s="14">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J18" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.985915492957</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-18.333333333333</v>
+        <v>-22.535211267605</v>
       </c>
       <c r="M18" s="15">
-        <v>48.484848484848</v>
+        <v>41.025641025641</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.522935779816</v>
+        <v>-77.822580645161</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>-26.315789473684</v>
+        <v>45.454545454545</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G19" s="14">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.594202898550</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="J19" s="14">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="K19" s="15">
-        <v>-2.068965517241</v>
+        <v>1.923076923076</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.960264900662</v>
+        <v>-4.790419161676</v>
       </c>
       <c r="M19" s="15">
-        <v>136.666666666667</v>
+        <v>144.615384615385</v>
       </c>
       <c r="N19" s="15">
-        <v>54.347826086956</v>
+        <v>63.917525773195</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
         <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>6.896551724137</v>
+        <v>8.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.428571428571</v>
+        <v>2.631578947368</v>
       </c>
       <c r="M20" s="15">
-        <v>72.222222222222</v>
+        <v>95</v>
       </c>
       <c r="N20" s="15">
-        <v>-68.686868686868</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-12.5</v>
+        <v>9.615384615384</v>
       </c>
       <c r="F21" s="17">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="G21" s="17">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.695652173913</v>
+        <v>-5.581395348837</v>
       </c>
       <c r="I21" s="17">
-        <v>475</v>
+        <v>539</v>
       </c>
       <c r="J21" s="17">
-        <v>475</v>
+        <v>527</v>
       </c>
       <c r="K21" s="18">
-        <v>0</v>
+        <v>2.277039848197</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.233870967741</v>
+        <v>-2.355072463768</v>
       </c>
       <c r="M21" s="18">
-        <v>94.672131147541</v>
+        <v>99.629629629629</v>
       </c>
       <c r="N21" s="18">
-        <v>-44.051825677267</v>
+        <v>-44.260599793174</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,40 +1180,40 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14">
         <v>2</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G22" s="14">
         <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I22" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>13.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>-35</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M22" s="15">
-        <v>62.5</v>
+        <v>88.888888888888</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.129032258064</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J23" s="14">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K23" s="15">
-        <v>-10.975609756097</v>
+        <v>1.176470588235</v>
       </c>
       <c r="L23" s="15">
-        <v>-2.666666666666</v>
+        <v>2.380952380952</v>
       </c>
       <c r="M23" s="15">
-        <v>62.222222222222</v>
+        <v>79.166666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1265,37 +1265,37 @@
         <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>-30</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G24" s="14">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H24" s="15">
-        <v>7.317073170731</v>
+        <v>9.375</v>
       </c>
       <c r="I24" s="14">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="J24" s="14">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="K24" s="15">
-        <v>-3.900709219858</v>
+        <v>-1.923076923076</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.902777777777</v>
+        <v>-3.164556962025</v>
       </c>
       <c r="M24" s="15">
-        <v>42.631578947368</v>
+        <v>47.826086956521</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>7.142857142857</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>19.148936170212</v>
+        <v>35.555555555555</v>
       </c>
       <c r="I25" s="14">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="J25" s="14">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.864406779661</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L25" s="15">
-        <v>-20</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E26" s="15">
-        <v>19.047619047619</v>
+        <v>73.684210526315</v>
       </c>
       <c r="F26" s="14">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="G26" s="14">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>25.842696629213</v>
       </c>
       <c r="I26" s="14">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="J26" s="14">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="K26" s="15">
-        <v>1.030927835051</v>
+        <v>6.103286384976</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.921568627450</v>
+        <v>0.892857142857</v>
       </c>
       <c r="M26" s="15">
-        <v>29.801324503311</v>
+        <v>30.635838150289</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1387,20 +1387,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>12</v>
@@ -1415,51 +1415,51 @@
         <v>71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H28" s="15">
-        <v>28.571428571428</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>22</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K28" s="15">
-        <v>29.411764705882</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1476,31 +1476,31 @@
         <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
         <v>-60</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1517,45 +1517,45 @@
         <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>6</v>
       </c>
       <c r="J30" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K30" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.310344827586</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="15">
         <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1610,20 +1610,20 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="14">
         <v>1</v>
       </c>
       <c r="H33" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>81</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -885,48 +885,48 @@
         <v>0</v>
       </c>
       <c r="N14" s="15">
-        <v>-94.444444444444</v>
+        <v>-95</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>42.857142857142</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>37.5</v>
       </c>
       <c r="M15" s="15">
-        <v>233.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-9.090909090909</v>
+        <v>-8.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>-10</v>
+        <v>37.5</v>
       </c>
       <c r="F16" s="14">
         <v>37</v>
       </c>
       <c r="G16" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>15.625</v>
+        <v>19.354838709677</v>
       </c>
       <c r="I16" s="14">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J16" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K16" s="15">
-        <v>5.063291139240</v>
+        <v>8.045977011494</v>
       </c>
       <c r="L16" s="15">
-        <v>-20.952380952381</v>
+        <v>-19.658119658119</v>
       </c>
       <c r="M16" s="15">
-        <v>16.901408450704</v>
+        <v>25.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-75</v>
+        <v>-73.669467787114</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
         <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>11.764705882352</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F17" s="14">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G17" s="14">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J17" s="14">
-        <v>169</v>
+        <v>186</v>
       </c>
       <c r="K17" s="15">
-        <v>13.609467455621</v>
+        <v>7.526881720430</v>
       </c>
       <c r="L17" s="15">
-        <v>17.791411042944</v>
+        <v>14.942528735632</v>
       </c>
       <c r="M17" s="15">
-        <v>170.422535211268</v>
+        <v>163.157894736842</v>
       </c>
       <c r="N17" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G18" s="14">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H18" s="15">
-        <v>-35.294117647058</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J18" s="14">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L18" s="15">
-        <v>-22.535211267605</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="M18" s="15">
-        <v>41.025641025641</v>
+        <v>46.341463414634</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.822580645161</v>
+        <v>-77.941176470588</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>45.454545454545</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F19" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G19" s="14">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>2.941176470588</v>
       </c>
       <c r="I19" s="14">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="J19" s="14">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="K19" s="15">
-        <v>1.923076923076</v>
+        <v>2.890173410404</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.790419161676</v>
+        <v>-2.197802197802</v>
       </c>
       <c r="M19" s="15">
-        <v>144.615384615385</v>
+        <v>157.971014492754</v>
       </c>
       <c r="N19" s="15">
-        <v>63.917525773195</v>
+        <v>67.924528301886</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
         <v>16</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-15.789473684210</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K20" s="15">
-        <v>8.333333333333</v>
+        <v>13.513513513513</v>
       </c>
       <c r="L20" s="15">
-        <v>2.631578947368</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="M20" s="15">
-        <v>95</v>
+        <v>82.608695652173</v>
       </c>
       <c r="N20" s="15">
-        <v>-66.666666666666</v>
+        <v>-67.441860465116</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,81 +1139,81 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E21" s="18">
-        <v>9.615384615384</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G21" s="17">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.581395348837</v>
+        <v>-5.238095238095</v>
       </c>
       <c r="I21" s="17">
-        <v>539</v>
+        <v>586</v>
       </c>
       <c r="J21" s="17">
-        <v>527</v>
+        <v>575</v>
       </c>
       <c r="K21" s="18">
-        <v>2.277039848197</v>
+        <v>1.913043478260</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.355072463768</v>
+        <v>-2.819237147595</v>
       </c>
       <c r="M21" s="18">
-        <v>99.629629629629</v>
+        <v>103.472222222222</v>
       </c>
       <c r="N21" s="18">
-        <v>-44.260599793174</v>
+        <v>-44.507575757575</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>4</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
         <v>2</v>
       </c>
       <c r="E22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>28.571428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>17</v>
       </c>
       <c r="J22" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K22" s="15">
-        <v>13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.727272727272</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M22" s="15">
         <v>88.888888888888</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G23" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H23" s="15">
-        <v>14.285714285714</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I23" s="14">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J23" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="K23" s="15">
-        <v>1.176470588235</v>
+        <v>-1.075268817204</v>
       </c>
       <c r="L23" s="15">
-        <v>2.380952380952</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="M23" s="15">
-        <v>79.166666666666</v>
+        <v>80.392156862745</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="F24" s="14">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G24" s="14">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H24" s="15">
-        <v>9.375</v>
+        <v>6.201550387596</v>
       </c>
       <c r="I24" s="14">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="J24" s="14">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.923076923076</v>
+        <v>-2.388059701492</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.164556962025</v>
+        <v>-6.837606837606</v>
       </c>
       <c r="M24" s="15">
-        <v>47.826086956521</v>
+        <v>46.636771300448</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-30</v>
       </c>
       <c r="F25" s="14">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G25" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H25" s="15">
-        <v>35.555555555555</v>
+        <v>12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J25" s="14">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.838709677419</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.940298507462</v>
+        <v>-14.482758620689</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,151 +1344,151 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D26" s="14">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E26" s="15">
-        <v>73.684210526315</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="F26" s="14">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G26" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="H26" s="15">
-        <v>25.842696629213</v>
+        <v>11.702127659574</v>
       </c>
       <c r="I26" s="14">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="J26" s="14">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="K26" s="15">
-        <v>6.103286384976</v>
+        <v>2.868852459016</v>
       </c>
       <c r="L26" s="15">
-        <v>0.892857142857</v>
+        <v>0.4</v>
       </c>
       <c r="M26" s="15">
-        <v>30.635838150289</v>
+        <v>31.413612565445</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="15">
-        <v>71.428571428571</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>6</v>
       </c>
       <c r="D28" s="14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H28" s="15">
-        <v>-41.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>-8.333333333333</v>
+        <v>7.692307692307</v>
       </c>
       <c r="L28" s="15">
-        <v>10</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F29" s="14">
         <v>2</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
         <v>0</v>
@@ -1497,39 +1497,39 @@
         <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.615384615384</v>
+        <v>-82.926829268292</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F30" s="14">
         <v>2</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K30" s="15">
         <v>0</v>
@@ -1538,10 +1538,10 @@
         <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-33.333333333333</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.25</v>
+        <v>-79.411764705882</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>81</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -892,35 +892,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13" t="s">
+      <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>11</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>57.142857142857</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>37.5</v>
+        <v>22.222222222222</v>
       </c>
       <c r="M15" s="15">
         <v>266.666666666667</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E16" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16" s="14">
         <v>31</v>
       </c>
       <c r="H16" s="15">
-        <v>19.354838709677</v>
+        <v>25.806451612903</v>
       </c>
       <c r="I16" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="J16" s="14">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="K16" s="15">
-        <v>8.045977011494</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.658119658119</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="M16" s="15">
-        <v>25.333333333333</v>
+        <v>21.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-73.669467787114</v>
+        <v>-74.307304785894</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E17" s="15">
-        <v>-52.941176470588</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="F17" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G17" s="14">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.084507042253</v>
       </c>
       <c r="I17" s="14">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="J17" s="14">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="K17" s="15">
-        <v>7.526881720430</v>
+        <v>3.349282296650</v>
       </c>
       <c r="L17" s="15">
-        <v>14.942528735632</v>
+        <v>10.769230769230</v>
       </c>
       <c r="M17" s="15">
-        <v>163.157894736842</v>
+        <v>154.117647058824</v>
       </c>
       <c r="N17" s="15">
-        <v>25</v>
+        <v>19.337016574585</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F18" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G18" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H18" s="15">
-        <v>-36.666666666666</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="I18" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J18" s="14">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K18" s="15">
-        <v>-26.829268292682</v>
+        <v>-31.868131868131</v>
       </c>
       <c r="L18" s="15">
-        <v>-21.052631578947</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M18" s="15">
-        <v>46.341463414634</v>
+        <v>44.186046511627</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.941176470588</v>
+        <v>-79.935275080906</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>16</v>
+      </c>
+      <c r="D19" s="14">
         <v>19</v>
       </c>
-      <c r="D19" s="14">
-        <v>17</v>
-      </c>
       <c r="E19" s="15">
-        <v>11.764705882352</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F19" s="14">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H19" s="15">
-        <v>2.941176470588</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="J19" s="14">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="K19" s="15">
-        <v>2.890173410404</v>
+        <v>2.604166666666</v>
       </c>
       <c r="L19" s="15">
-        <v>-2.197802197802</v>
+        <v>-0.505050505050</v>
       </c>
       <c r="M19" s="15">
-        <v>157.971014492754</v>
+        <v>152.564102564103</v>
       </c>
       <c r="N19" s="15">
-        <v>67.924528301886</v>
+        <v>71.304347826087</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>3</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I20" s="14">
         <v>42</v>
       </c>
       <c r="J20" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K20" s="15">
-        <v>13.513513513513</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-2.325581395348</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="M20" s="15">
         <v>82.608695652173</v>
       </c>
       <c r="N20" s="15">
-        <v>-67.441860465116</v>
+        <v>-70.422535211267</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D21" s="17">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-2.083333333333</v>
+        <v>-37.313432835820</v>
       </c>
       <c r="F21" s="17">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G21" s="17">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.238095238095</v>
+        <v>-9.767441860465</v>
       </c>
       <c r="I21" s="17">
-        <v>586</v>
+        <v>631</v>
       </c>
       <c r="J21" s="17">
-        <v>575</v>
+        <v>642</v>
       </c>
       <c r="K21" s="18">
-        <v>1.913043478260</v>
+        <v>-1.713395638629</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.819237147595</v>
+        <v>-4.248861911987</v>
       </c>
       <c r="M21" s="18">
-        <v>103.472222222222</v>
+        <v>99.053627760252</v>
       </c>
       <c r="N21" s="18">
-        <v>-44.507575757575</v>
+        <v>-46.343537414966</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F22" s="14">
         <v>7</v>
@@ -1198,19 +1198,19 @@
         <v>16.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J22" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-26.086956521739</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M22" s="15">
-        <v>88.888888888888</v>
+        <v>80</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F23" s="14">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G23" s="14">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H23" s="15">
-        <v>11.111111111111</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J23" s="14">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K23" s="15">
-        <v>-1.075268817204</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="15">
-        <v>-2.127659574468</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="M23" s="15">
-        <v>80.392156862745</v>
+        <v>72.727272727272</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D24" s="14">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E24" s="15">
-        <v>-8.695652173913</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="G24" s="14">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="H24" s="15">
-        <v>6.201550387596</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I24" s="14">
-        <v>327</v>
+        <v>363</v>
       </c>
       <c r="J24" s="14">
-        <v>335</v>
+        <v>372</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.388059701492</v>
+        <v>-2.419354838709</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.837606837606</v>
+        <v>-4.473684210526</v>
       </c>
       <c r="M24" s="15">
-        <v>46.636771300448</v>
+        <v>51.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G25" s="14">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="J25" s="14">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.462686567164</v>
+        <v>-9.589041095890</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.482758620689</v>
+        <v>-15.923566878980</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D26" s="14">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.129032258064</v>
+        <v>17.241379310344</v>
       </c>
       <c r="F26" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G26" s="14">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="H26" s="15">
-        <v>11.702127659574</v>
+        <v>16</v>
       </c>
       <c r="I26" s="14">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="J26" s="14">
-        <v>244</v>
+        <v>273</v>
       </c>
       <c r="K26" s="15">
-        <v>2.868852459016</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L26" s="15">
-        <v>0.4</v>
+        <v>4.379562043795</v>
       </c>
       <c r="M26" s="15">
-        <v>31.413612565445</v>
+        <v>34.905660377358</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>3</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
         <v>13</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>62.5</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L27" s="15">
-        <v>18.181818181818</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>6</v>
-      </c>
-      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>200</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-30.769230769230</v>
+        <v>-10</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
         <v>26</v>
       </c>
       <c r="K28" s="15">
-        <v>7.692307692307</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L28" s="15">
-        <v>27.272727272727</v>
+        <v>-6.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,23 +1466,23 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>0</v>
-      </c>
-      <c r="F29" s="14">
-        <v>2</v>
-      </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1494,36 +1494,36 @@
         <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M29" s="15">
-        <v>-53.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="N29" s="15">
-        <v>-82.926829268292</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>0</v>
-      </c>
-      <c r="F30" s="14">
-        <v>2</v>
-      </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
@@ -1535,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M30" s="15">
-        <v>-22.222222222222</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="N30" s="15">
-        <v>-79.411764705882</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -879,54 +879,54 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
+        <v>-75</v>
+      </c>
+      <c r="M14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
       <c r="N14" s="15">
-        <v>-95</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
         <v>-50</v>
       </c>
       <c r="I15" s="14">
+        <v>12</v>
+      </c>
+      <c r="J15" s="14">
         <v>11</v>
       </c>
-      <c r="J15" s="14">
-        <v>9</v>
-      </c>
       <c r="K15" s="15">
-        <v>22.222222222222</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L15" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="M15" s="15">
-        <v>266.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-8.333333333333</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E16" s="15">
-        <v>33.333333333333</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F16" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G16" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>25.806451612903</v>
+        <v>16.216216216216</v>
       </c>
       <c r="I16" s="14">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="J16" s="14">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="K16" s="15">
-        <v>9.677419354838</v>
+        <v>10.377358490566</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.047619047619</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="M16" s="15">
-        <v>21.428571428571</v>
+        <v>19.387755102040</v>
       </c>
       <c r="N16" s="15">
-        <v>-74.307304785894</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D17" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E17" s="15">
-        <v>-30.434782608695</v>
+        <v>-10</v>
       </c>
       <c r="F17" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="G17" s="14">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.084507042253</v>
+        <v>-18.390804597701</v>
       </c>
       <c r="I17" s="14">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="J17" s="14">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="K17" s="15">
-        <v>3.349282296650</v>
+        <v>1.673640167364</v>
       </c>
       <c r="L17" s="15">
-        <v>10.769230769230</v>
+        <v>8.482142857142</v>
       </c>
       <c r="M17" s="15">
-        <v>154.117647058824</v>
+        <v>167.032967032967</v>
       </c>
       <c r="N17" s="15">
-        <v>19.337016574585</v>
+        <v>15.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-77.777777777777</v>
+        <v>-12.5</v>
       </c>
       <c r="F18" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G18" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H18" s="15">
-        <v>-48.148148148148</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="J18" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.868131868131</v>
+        <v>-29.292929292929</v>
       </c>
       <c r="L18" s="15">
-        <v>-24.390243902439</v>
+        <v>-20.454545454545</v>
       </c>
       <c r="M18" s="15">
-        <v>44.186046511627</v>
+        <v>42.857142857142</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.935275080906</v>
+        <v>-79.041916167664</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-15.789473684210</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="F19" s="14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G19" s="14">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H19" s="15">
-        <v>3.030303030303</v>
+        <v>9.836065573770</v>
       </c>
       <c r="I19" s="14">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="J19" s="14">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K19" s="15">
-        <v>2.604166666666</v>
+        <v>2.427184466019</v>
       </c>
       <c r="L19" s="15">
-        <v>-0.505050505050</v>
+        <v>-4.524886877828</v>
       </c>
       <c r="M19" s="15">
-        <v>152.564102564103</v>
+        <v>157.317073170732</v>
       </c>
       <c r="N19" s="15">
-        <v>71.304347826087</v>
+        <v>72.950819672131</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-35.294117647058</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="I20" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="J20" s="14">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K20" s="15">
-        <v>-6.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-8.695652173913</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="M20" s="15">
-        <v>82.608695652173</v>
+        <v>91.304347826087</v>
       </c>
       <c r="N20" s="15">
-        <v>-70.422535211267</v>
+        <v>-72.5</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E21" s="18">
-        <v>-37.313432835820</v>
+        <v>-15.584415584415</v>
       </c>
       <c r="F21" s="17">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="G21" s="17">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.767441860465</v>
+        <v>-11.475409836065</v>
       </c>
       <c r="I21" s="17">
-        <v>631</v>
+        <v>698</v>
       </c>
       <c r="J21" s="17">
-        <v>642</v>
+        <v>719</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.713395638629</v>
+        <v>-2.920723226703</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.248861911987</v>
+        <v>-4.904632152588</v>
       </c>
       <c r="M21" s="18">
-        <v>99.053627760252</v>
+        <v>99.428571428571</v>
       </c>
       <c r="N21" s="18">
-        <v>-46.343537414966</v>
+        <v>-45.891472868217</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>16.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I22" s="14">
         <v>18</v>
       </c>
       <c r="J22" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L22" s="15">
         <v>-21.739130434782</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D23" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15">
-        <v>-71.428571428571</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F23" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G23" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H23" s="15">
-        <v>8.333333333333</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I23" s="14">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="J23" s="14">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K23" s="15">
-        <v>-5</v>
+        <v>-6.194690265486</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.844036697247</v>
+        <v>-12.396694214876</v>
       </c>
       <c r="M23" s="15">
-        <v>72.727272727272</v>
+        <v>70.967741935483</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D24" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" s="15">
+        <v>30.769230769230</v>
+      </c>
+      <c r="F24" s="14">
+        <v>143</v>
+      </c>
+      <c r="G24" s="14">
+        <v>129</v>
+      </c>
+      <c r="H24" s="15">
+        <v>10.852713178294</v>
+      </c>
+      <c r="I24" s="14">
+        <v>413</v>
+      </c>
+      <c r="J24" s="14">
+        <v>411</v>
+      </c>
+      <c r="K24" s="15">
+        <v>0.486618004866</v>
+      </c>
+      <c r="L24" s="15">
         <v>0</v>
       </c>
-      <c r="F24" s="14">
-        <v>128</v>
-      </c>
-      <c r="G24" s="14">
-        <v>140</v>
-      </c>
-      <c r="H24" s="15">
-        <v>-8.571428571428</v>
-      </c>
-      <c r="I24" s="14">
-        <v>363</v>
-      </c>
-      <c r="J24" s="14">
-        <v>372</v>
-      </c>
-      <c r="K24" s="15">
-        <v>-2.419354838709</v>
-      </c>
-      <c r="L24" s="15">
-        <v>-4.473684210526</v>
-      </c>
       <c r="M24" s="15">
-        <v>51.25</v>
+        <v>53.531598513011</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F25" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>4.444444444444</v>
       </c>
       <c r="I25" s="14">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="J25" s="14">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.589041095890</v>
+        <v>-6.748466257668</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.923566878980</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>34</v>
       </c>
       <c r="D26" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E26" s="15">
-        <v>17.241379310344</v>
+        <v>25.925925925925</v>
       </c>
       <c r="F26" s="14">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="G26" s="14">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="H26" s="15">
-        <v>16</v>
+        <v>20.754716981132</v>
       </c>
       <c r="I26" s="14">
-        <v>286</v>
+        <v>321</v>
       </c>
       <c r="J26" s="14">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="K26" s="15">
-        <v>4.761904761904</v>
+        <v>7</v>
       </c>
       <c r="L26" s="15">
-        <v>4.379562043795</v>
+        <v>9.183673469387</v>
       </c>
       <c r="M26" s="15">
-        <v>34.905660377358</v>
+        <v>37.768240343347</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>3</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-10</v>
+        <v>20</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K28" s="15">
-        <v>15.384615384615</v>
+        <v>25.925925925925</v>
       </c>
       <c r="L28" s="15">
-        <v>-6.25</v>
+        <v>3.030303030303</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,38 +1469,38 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M29" s="15">
         <v>-58.823529411764</v>
       </c>
       <c r="N29" s="15">
-        <v>-83.333333333333</v>
+        <v>-84.090909090909</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,38 +1510,38 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
       </c>
       <c r="J30" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M30" s="15">
         <v>-36.363636363636</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-81.081081081081</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1619,11 +1619,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="14">
         <v>1</v>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>9.090909090909</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>20</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="N15" s="15">
-        <v>-14.285714285714</v>
+        <v>-13.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="15">
-        <v>15.384615384615</v>
+        <v>75</v>
       </c>
       <c r="F16" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H16" s="15">
-        <v>16.216216216216</v>
+        <v>37.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="J16" s="14">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="K16" s="15">
-        <v>10.377358490566</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.217391304347</v>
+        <v>-12.5</v>
       </c>
       <c r="M16" s="15">
-        <v>19.387755102040</v>
+        <v>27.884615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.727272727272</v>
+        <v>-71.581196581196</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D17" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E17" s="15">
-        <v>-10</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G17" s="14">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H17" s="15">
-        <v>-18.390804597701</v>
+        <v>-31.914893617021</v>
       </c>
       <c r="I17" s="14">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="J17" s="14">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="K17" s="15">
-        <v>1.673640167364</v>
+        <v>-1.520912547528</v>
       </c>
       <c r="L17" s="15">
-        <v>8.482142857142</v>
+        <v>4.858299595141</v>
       </c>
       <c r="M17" s="15">
-        <v>167.032967032967</v>
+        <v>169.791666666667</v>
       </c>
       <c r="N17" s="15">
-        <v>15.714285714285</v>
+        <v>8.368200836820</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>7</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="15">
-        <v>-12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="14">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>-25.806451612903</v>
       </c>
       <c r="I18" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="J18" s="14">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K18" s="15">
-        <v>-29.292929292929</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-20.454545454545</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M18" s="15">
-        <v>42.857142857142</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.041916167664</v>
+        <v>-77.903682719546</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-7.142857142857</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F19" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G19" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H19" s="15">
-        <v>9.836065573770</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="J19" s="14">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="K19" s="15">
-        <v>2.427184466019</v>
+        <v>3.125</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.524886877828</v>
+        <v>-1.702127659574</v>
       </c>
       <c r="M19" s="15">
-        <v>157.317073170732</v>
+        <v>159.550561797753</v>
       </c>
       <c r="N19" s="15">
-        <v>72.950819672131</v>
+        <v>63.829787234042</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-53.846153846153</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J20" s="14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K20" s="15">
         <v>-20</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.204081632653</v>
+        <v>-4</v>
       </c>
       <c r="M20" s="15">
-        <v>91.304347826087</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.5</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D21" s="17">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.584415584415</v>
+        <v>-20.895522388059</v>
       </c>
       <c r="F21" s="17">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G21" s="17">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.475409836065</v>
+        <v>-16.988416988417</v>
       </c>
       <c r="I21" s="17">
-        <v>698</v>
+        <v>763</v>
       </c>
       <c r="J21" s="17">
-        <v>719</v>
+        <v>786</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.920723226703</v>
+        <v>-2.926208651399</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.904632152588</v>
+        <v>-3.417721518987</v>
       </c>
       <c r="M21" s="18">
-        <v>99.428571428571</v>
+        <v>105.660377358491</v>
       </c>
       <c r="N21" s="18">
-        <v>-45.891472868217</v>
+        <v>-46.001415428167</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="14">
+        <v>2</v>
+      </c>
+      <c r="D22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>3</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>5</v>
-      </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J22" s="14">
         <v>21</v>
       </c>
       <c r="K22" s="15">
-        <v>-14.285714285714</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L22" s="15">
-        <v>-21.739130434782</v>
+        <v>-20</v>
       </c>
       <c r="M22" s="15">
-        <v>80</v>
+        <v>81.818181818181</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E23" s="15">
-        <v>-23.076923076923</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F23" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G23" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="H23" s="15">
-        <v>3.225806451612</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="I23" s="14">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="J23" s="14">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.194690265486</v>
+        <v>-0.806451612903</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.396694214876</v>
+        <v>-3.149606299212</v>
       </c>
       <c r="M23" s="15">
-        <v>70.967741935483</v>
+        <v>86.363636363636</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="D24" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>30.769230769230</v>
+        <v>2.941176470588</v>
       </c>
       <c r="F24" s="14">
         <v>143</v>
       </c>
       <c r="G24" s="14">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H24" s="15">
-        <v>10.852713178294</v>
+        <v>7.518796992481</v>
       </c>
       <c r="I24" s="14">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="J24" s="14">
-        <v>411</v>
+        <v>445</v>
       </c>
       <c r="K24" s="15">
-        <v>0.486618004866</v>
+        <v>0.224719101123</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>2.764976958525</v>
       </c>
       <c r="M24" s="15">
-        <v>53.531598513011</v>
+        <v>50.675675675675</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E25" s="15">
-        <v>5.882352941176</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G25" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>4.444444444444</v>
+        <v>-15.686274509803</v>
       </c>
       <c r="I25" s="14">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J25" s="14">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.748466257668</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.627906976744</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E26" s="15">
-        <v>25.925925925925</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G26" s="14">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H26" s="15">
-        <v>20.754716981132</v>
+        <v>13.888888888888</v>
       </c>
       <c r="I26" s="14">
+        <v>346</v>
+      </c>
+      <c r="J26" s="14">
         <v>321</v>
       </c>
-      <c r="J26" s="14">
-        <v>300</v>
-      </c>
       <c r="K26" s="15">
-        <v>7</v>
+        <v>7.788161993769</v>
       </c>
       <c r="L26" s="15">
-        <v>9.183673469387</v>
+        <v>13.815789473684</v>
       </c>
       <c r="M26" s="15">
-        <v>37.768240343347</v>
+        <v>37.848605577689</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,25 +1394,25 @@
         <v>-66.666666666666</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
         <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K28" s="15">
-        <v>25.925925925925</v>
+        <v>25</v>
       </c>
       <c r="L28" s="15">
-        <v>3.030303030303</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,20 +1469,20 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1500,7 +1500,7 @@
         <v>-58.823529411764</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.090909090909</v>
+        <v>-84.444444444444</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,20 +1510,20 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
@@ -1541,7 +1541,7 @@
         <v>-36.363636363636</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.081081081081</v>
+        <v>-81.578947368421</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,29 +1610,29 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
+      <c r="D33" s="14">
+        <v>1</v>
+      </c>
+      <c r="E33" s="15">
+        <v>-100</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>21</v>
+      <c r="G33" s="14">
+        <v>1</v>
+      </c>
+      <c r="H33" s="15">
+        <v>-100</v>
       </c>
       <c r="I33" s="14">
         <v>1</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L33" s="15">
         <v>0</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H15" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K15" s="15">
-        <v>-7.142857142857</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="15">
-        <v>18.181818181818</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M15" s="15">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="N15" s="15">
-        <v>-13.333333333333</v>
+        <v>-6.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
-        <v>37.142857142857</v>
+        <v>27.027027027027</v>
       </c>
       <c r="I16" s="14">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="J16" s="14">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="K16" s="15">
-        <v>16.666666666666</v>
+        <v>15.322580645161</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.5</v>
+        <v>-12.804878048780</v>
       </c>
       <c r="M16" s="15">
-        <v>27.884615384615</v>
+        <v>27.678571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-71.581196581196</v>
+        <v>-71.457085828343</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F17" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G17" s="14">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.914893617021</v>
+        <v>-31.25</v>
       </c>
       <c r="I17" s="14">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="J17" s="14">
-        <v>263</v>
+        <v>282</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.520912547528</v>
+        <v>-3.900709219858</v>
       </c>
       <c r="L17" s="15">
-        <v>4.858299595141</v>
+        <v>2.264150943396</v>
       </c>
       <c r="M17" s="15">
-        <v>169.791666666667</v>
+        <v>171</v>
       </c>
       <c r="N17" s="15">
-        <v>8.368200836820</v>
+        <v>-1.094890510948</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="15">
-        <v>-22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="F18" s="14">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G18" s="14">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H18" s="15">
-        <v>-25.806451612903</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I18" s="14">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="J18" s="14">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.777777777777</v>
+        <v>-22.881355932203</v>
       </c>
       <c r="L18" s="15">
-        <v>-14.285714285714</v>
+        <v>-5.208333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>52.941176470588</v>
+        <v>62.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.903682719546</v>
+        <v>-75.471698113207</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>-68</v>
       </c>
       <c r="F19" s="14">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G19" s="14">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="I19" s="14">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="J19" s="14">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="K19" s="15">
-        <v>3.125</v>
+        <v>-3.614457831325</v>
       </c>
       <c r="L19" s="15">
-        <v>-1.702127659574</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M19" s="15">
-        <v>159.550561797753</v>
+        <v>147.422680412371</v>
       </c>
       <c r="N19" s="15">
-        <v>63.829787234042</v>
+        <v>48.148148148148</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="I20" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J20" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K20" s="15">
-        <v>-20</v>
+        <v>-18.461538461538</v>
       </c>
       <c r="L20" s="15">
-        <v>-4</v>
+        <v>-5.357142857142</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>103.846153846154</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.727272727272</v>
+        <v>-71.505376344086</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D21" s="17">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E21" s="18">
-        <v>-20.895522388059</v>
+        <v>-36.619718309859</v>
       </c>
       <c r="F21" s="17">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G21" s="17">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.988416988417</v>
+        <v>-24.113475177305</v>
       </c>
       <c r="I21" s="17">
-        <v>763</v>
+        <v>813</v>
       </c>
       <c r="J21" s="17">
-        <v>786</v>
+        <v>857</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.926208651399</v>
+        <v>-5.134189031505</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.417721518987</v>
+        <v>-4.465334900117</v>
       </c>
       <c r="M21" s="18">
-        <v>105.660377358491</v>
+        <v>103.759398496241</v>
       </c>
       <c r="N21" s="18">
-        <v>-46.001415428167</v>
+        <v>-46.862745098039</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
+      <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I22" s="14">
         <v>20</v>
       </c>
       <c r="J22" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K22" s="15">
-        <v>-4.761904761904</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L22" s="15">
         <v>-20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E23" s="15">
-        <v>-18.181818181818</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F23" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H23" s="15">
-        <v>-25.641025641025</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="I23" s="14">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J23" s="14">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="K23" s="15">
-        <v>-0.806451612903</v>
+        <v>-3.649635036496</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.149606299212</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M23" s="15">
-        <v>86.363636363636</v>
+        <v>97.014925373134</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D24" s="14">
         <v>34</v>
       </c>
       <c r="E24" s="15">
-        <v>2.941176470588</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="G24" s="14">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="H24" s="15">
-        <v>7.518796992481</v>
+        <v>15.972222222222</v>
       </c>
       <c r="I24" s="14">
-        <v>446</v>
+        <v>492</v>
       </c>
       <c r="J24" s="14">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="K24" s="15">
-        <v>0.224719101123</v>
+        <v>2.713987473903</v>
       </c>
       <c r="L24" s="15">
-        <v>2.764976958525</v>
+        <v>6.724511930585</v>
       </c>
       <c r="M24" s="15">
-        <v>50.675675675675</v>
+        <v>53.75</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D25" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-33.333333333333</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="F25" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-15.686274509803</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="14">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="J25" s="14">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.571428571428</v>
+        <v>-8.762886597938</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.111111111111</v>
+        <v>-6.842105263157</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>28</v>
       </c>
       <c r="D26" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>21.739130434782</v>
       </c>
       <c r="F26" s="14">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G26" s="14">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H26" s="15">
-        <v>13.888888888888</v>
+        <v>24</v>
       </c>
       <c r="I26" s="14">
-        <v>346</v>
+        <v>372</v>
       </c>
       <c r="J26" s="14">
-        <v>321</v>
+        <v>344</v>
       </c>
       <c r="K26" s="15">
-        <v>7.788161993769</v>
+        <v>8.139534883720</v>
       </c>
       <c r="L26" s="15">
-        <v>13.815789473684</v>
+        <v>13.761467889908</v>
       </c>
       <c r="M26" s="15">
-        <v>37.848605577689</v>
+        <v>34.296028880866</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,22 +1397,22 @@
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K27" s="15">
-        <v>-11.764705882352</v>
+        <v>-15</v>
       </c>
       <c r="L27" s="15">
-        <v>-6.25</v>
+        <v>6.25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="F28" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>225</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I28" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K28" s="15">
-        <v>25</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-2.777777777777</v>
+        <v>-10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
@@ -1494,13 +1494,13 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L29" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M29" s="15">
         <v>-58.823529411764</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.444444444444</v>
+        <v>-85.416666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>7</v>
@@ -1535,13 +1535,13 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L30" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M30" s="15">
         <v>-36.363636363636</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.578947368421</v>
+        <v>-82.926829268292</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1610,11 +1610,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,22 +870,22 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="14">
         <v>3</v>
       </c>
       <c r="K14" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L14" s="15">
         <v>-66.666666666666</v>
       </c>
-      <c r="L14" s="15">
-        <v>-75</v>
-      </c>
       <c r="M14" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-95.238095238095</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -896,37 +896,37 @@
         <v>1</v>
       </c>
       <c r="D15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>8</v>
+      </c>
+      <c r="H15" s="15">
         <v>-50</v>
       </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>9</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J15" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K15" s="15">
-        <v>-12.5</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L15" s="15">
-        <v>27.272727272727</v>
+        <v>25</v>
       </c>
       <c r="M15" s="15">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-6.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>8.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H16" s="15">
-        <v>27.027027027027</v>
+        <v>20.930232558139</v>
       </c>
       <c r="I16" s="14">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="J16" s="14">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K16" s="15">
-        <v>15.322580645161</v>
+        <v>14.705882352941</v>
       </c>
       <c r="L16" s="15">
-        <v>-12.804878048780</v>
+        <v>-8.235294117647</v>
       </c>
       <c r="M16" s="15">
-        <v>27.678571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-71.457085828343</v>
+        <v>-71.480804387568</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.105263157894</v>
+        <v>9.523809523809</v>
       </c>
       <c r="F17" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G17" s="14">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.25</v>
+        <v>-21.276595744680</v>
       </c>
       <c r="I17" s="14">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="J17" s="14">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.900709219858</v>
+        <v>-2.640264026402</v>
       </c>
       <c r="L17" s="15">
-        <v>2.264150943396</v>
+        <v>2.787456445993</v>
       </c>
       <c r="M17" s="15">
-        <v>171</v>
+        <v>173.148148148148</v>
       </c>
       <c r="N17" s="15">
-        <v>-1.094890510948</v>
+        <v>1.374570446735</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>10</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G18" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H18" s="15">
-        <v>-13.888888888888</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J18" s="14">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.881355932203</v>
+        <v>-22.580645161290</v>
       </c>
       <c r="L18" s="15">
-        <v>-5.208333333333</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>62.5</v>
+        <v>62.711864406779</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.471698113207</v>
+        <v>-76.178660049627</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E19" s="15">
-        <v>-68</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G19" s="14">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H19" s="15">
-        <v>-26.315789473684</v>
+        <v>-29.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.614457831325</v>
+        <v>-4.868913857677</v>
       </c>
       <c r="L19" s="15">
-        <v>-5.882352941176</v>
+        <v>-4.868913857677</v>
       </c>
       <c r="M19" s="15">
-        <v>147.422680412371</v>
+        <v>128.828828828829</v>
       </c>
       <c r="N19" s="15">
-        <v>48.148148148148</v>
+        <v>39.560439560439</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-37.5</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
         <v>28</v>
       </c>
       <c r="H20" s="15">
-        <v>-60.714285714285</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J20" s="14">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.461538461538</v>
+        <v>-20.547945205479</v>
       </c>
       <c r="L20" s="15">
-        <v>-5.357142857142</v>
+        <v>-7.936507936507</v>
       </c>
       <c r="M20" s="15">
-        <v>103.846153846154</v>
+        <v>100</v>
       </c>
       <c r="N20" s="15">
-        <v>-71.505376344086</v>
+        <v>-71.844660194174</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="D21" s="17">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.619718309859</v>
+        <v>-7.575757575757</v>
       </c>
       <c r="F21" s="17">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="G21" s="17">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H21" s="18">
-        <v>-24.113475177305</v>
+        <v>-17.081850533807</v>
       </c>
       <c r="I21" s="17">
-        <v>813</v>
+        <v>876</v>
       </c>
       <c r="J21" s="17">
-        <v>857</v>
+        <v>923</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.134189031505</v>
+        <v>-5.092091007583</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.465334900117</v>
+        <v>-3.736263736263</v>
       </c>
       <c r="M21" s="18">
-        <v>103.759398496241</v>
+        <v>102.777777777778</v>
       </c>
       <c r="N21" s="18">
-        <v>-46.862745098039</v>
+        <v>-47.513481126423</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H22" s="15">
-        <v>-40</v>
+        <v>-62.5</v>
       </c>
       <c r="I22" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J22" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K22" s="15">
-        <v>-9.090909090909</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="L22" s="15">
-        <v>-20</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="M22" s="15">
-        <v>81.818181818181</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="15">
-        <v>-38.461538461538</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G23" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="H23" s="15">
-        <v>-31.818181818181</v>
+        <v>-32.653061224489</v>
       </c>
       <c r="I23" s="14">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="J23" s="14">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="K23" s="15">
-        <v>-3.649635036496</v>
+        <v>-7.382550335570</v>
       </c>
       <c r="L23" s="15">
-        <v>-6.382978723404</v>
+        <v>-7.382550335570</v>
       </c>
       <c r="M23" s="15">
-        <v>97.014925373134</v>
+        <v>97.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E24" s="15">
-        <v>41.176470588235</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G24" s="14">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H24" s="15">
-        <v>15.972222222222</v>
+        <v>15.909090909090</v>
       </c>
       <c r="I24" s="14">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="J24" s="14">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="K24" s="15">
-        <v>2.713987473903</v>
+        <v>1.984126984126</v>
       </c>
       <c r="L24" s="15">
-        <v>6.724511930585</v>
+        <v>2.594810379241</v>
       </c>
       <c r="M24" s="15">
-        <v>53.75</v>
+        <v>45.609065155807</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>-15.789473684210</v>
+        <v>75</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>-15</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I25" s="14">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="J25" s="14">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="K25" s="15">
-        <v>-8.762886597938</v>
+        <v>-7.070707070707</v>
       </c>
       <c r="L25" s="15">
-        <v>-6.842105263157</v>
+        <v>-13.615023474178</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>43</v>
+      </c>
+      <c r="D26" s="14">
         <v>28</v>
       </c>
-      <c r="D26" s="14">
-        <v>23</v>
-      </c>
       <c r="E26" s="15">
-        <v>21.739130434782</v>
+        <v>53.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="G26" s="14">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H26" s="15">
-        <v>24</v>
+        <v>37.373737373737</v>
       </c>
       <c r="I26" s="14">
+        <v>418</v>
+      </c>
+      <c r="J26" s="14">
         <v>372</v>
       </c>
-      <c r="J26" s="14">
-        <v>344</v>
-      </c>
       <c r="K26" s="15">
-        <v>8.139534883720</v>
+        <v>12.365591397849</v>
       </c>
       <c r="L26" s="15">
-        <v>13.761467889908</v>
+        <v>20.809248554913</v>
       </c>
       <c r="M26" s="15">
-        <v>34.296028880866</v>
+        <v>39.333333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="I27" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J27" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" s="15">
-        <v>-15</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
+        <v>37</v>
+      </c>
+      <c r="J28" s="14">
         <v>36</v>
       </c>
-      <c r="J28" s="14">
-        <v>33</v>
-      </c>
       <c r="K28" s="15">
-        <v>9.090909090909</v>
+        <v>2.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>-10</v>
+        <v>-13.953488372093</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14">
+        <v>2</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K29" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L29" s="15">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-58.823529411764</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.416666666666</v>
+        <v>-84.313725490196</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K30" s="15">
-        <v>-22.222222222222</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L30" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M30" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N30" s="15">
-        <v>-82.926829268292</v>
+        <v>-81.818181818181</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -851,32 +851,32 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>2</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-50</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K14" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="L14" s="15">
         <v>-66.666666666666</v>
@@ -885,335 +885,335 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.304347826087</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
+        <v>100</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
+        <v>7</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-14.285714285714</v>
+      </c>
+      <c r="I15" s="14">
+        <v>18</v>
+      </c>
+      <c r="J15" s="14">
+        <v>18</v>
+      </c>
+      <c r="K15" s="15">
         <v>0</v>
       </c>
-      <c r="F15" s="14">
-        <v>4</v>
-      </c>
-      <c r="G15" s="14">
-        <v>8</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-50</v>
-      </c>
-      <c r="I15" s="14">
-        <v>15</v>
-      </c>
-      <c r="J15" s="14">
-        <v>17</v>
-      </c>
-      <c r="K15" s="15">
-        <v>-11.764705882352</v>
-      </c>
       <c r="L15" s="15">
-        <v>25</v>
+        <v>38.461538461538</v>
       </c>
       <c r="M15" s="15">
         <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E16" s="15">
-        <v>8.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F16" s="14">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G16" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H16" s="15">
-        <v>20.930232558139</v>
+        <v>2.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J16" s="14">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="K16" s="15">
-        <v>14.705882352941</v>
+        <v>9.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-8.235294117647</v>
+        <v>-7.344632768361</v>
       </c>
       <c r="M16" s="15">
-        <v>33.333333333333</v>
+        <v>32.258064516129</v>
       </c>
       <c r="N16" s="15">
-        <v>-71.480804387568</v>
+        <v>-72.156196943972</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D17" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E17" s="15">
-        <v>9.523809523809</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F17" s="14">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="G17" s="14">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.276595744680</v>
+        <v>-27.710843373494</v>
       </c>
       <c r="I17" s="14">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="J17" s="14">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.640264026402</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L17" s="15">
-        <v>2.787456445993</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
-        <v>173.148148148148</v>
+        <v>161.016949152542</v>
       </c>
       <c r="N17" s="15">
-        <v>1.374570446735</v>
+        <v>-3.144654088050</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F18" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J18" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.580645161290</v>
+        <v>-25.185185185185</v>
       </c>
       <c r="L18" s="15">
-        <v>-8.571428571428</v>
+        <v>-7.339449541284</v>
       </c>
       <c r="M18" s="15">
-        <v>62.711864406779</v>
+        <v>68.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.178660049627</v>
+        <v>-76.066350710900</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>5.882352941176</v>
       </c>
       <c r="F19" s="14">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G19" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.333333333333</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="I19" s="14">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="J19" s="14">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.868913857677</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="L19" s="15">
-        <v>-4.868913857677</v>
+        <v>-6.529209621993</v>
       </c>
       <c r="M19" s="15">
-        <v>128.828828828829</v>
+        <v>122.950819672131</v>
       </c>
       <c r="N19" s="15">
-        <v>39.560439560439</v>
+        <v>43.157894736842</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>9</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-77.777777777777</v>
+      </c>
+      <c r="F20" s="14">
+        <v>15</v>
+      </c>
+      <c r="G20" s="14">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>5</v>
-      </c>
-      <c r="D20" s="14">
-        <v>8</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-37.5</v>
-      </c>
-      <c r="F20" s="14">
-        <v>16</v>
-      </c>
-      <c r="G20" s="14">
-        <v>28</v>
-      </c>
       <c r="H20" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J20" s="14">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K20" s="15">
-        <v>-20.547945205479</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="L20" s="15">
-        <v>-7.936507936507</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M20" s="15">
-        <v>100</v>
+        <v>93.548387096774</v>
       </c>
       <c r="N20" s="15">
-        <v>-71.844660194174</v>
+        <v>-72.093023255813</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D21" s="17">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E21" s="18">
-        <v>-7.575757575757</v>
+        <v>-36.986301369863</v>
       </c>
       <c r="F21" s="17">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="G21" s="17">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.081850533807</v>
+        <v>-22.382671480144</v>
       </c>
       <c r="I21" s="17">
-        <v>876</v>
+        <v>925</v>
       </c>
       <c r="J21" s="17">
-        <v>923</v>
+        <v>996</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.092091007583</v>
+        <v>-7.128514056224</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.736263736263</v>
+        <v>-4.933196300102</v>
       </c>
       <c r="M21" s="18">
-        <v>102.777777777778</v>
+        <v>99.353448275862</v>
       </c>
       <c r="N21" s="18">
-        <v>-47.513481126423</v>
+        <v>-47.916666666666</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C22" s="14">
+        <v>28</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>4</v>
-      </c>
       <c r="E22" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-62.5</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>21</v>
       </c>
       <c r="J22" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K22" s="15">
-        <v>-19.230769230769</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>-19.230769230769</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E23" s="15">
-        <v>-50</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F23" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G23" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H23" s="15">
-        <v>-32.653061224489</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="I23" s="14">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J23" s="14">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="K23" s="15">
-        <v>-7.382550335570</v>
+        <v>-13.253012048192</v>
       </c>
       <c r="L23" s="15">
-        <v>-7.382550335570</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="M23" s="15">
-        <v>97.142857142857</v>
+        <v>89.473684210526</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D24" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="F24" s="14">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G24" s="14">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="H24" s="15">
-        <v>15.909090909090</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I24" s="14">
-        <v>514</v>
+        <v>542</v>
       </c>
       <c r="J24" s="14">
-        <v>504</v>
+        <v>535</v>
       </c>
       <c r="K24" s="15">
-        <v>1.984126984126</v>
+        <v>1.308411214953</v>
       </c>
       <c r="L24" s="15">
-        <v>2.594810379241</v>
+        <v>4.230769230769</v>
       </c>
       <c r="M24" s="15">
-        <v>45.609065155807</v>
+        <v>44.533333333333</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>75</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="F25" s="14">
+        <v>48</v>
+      </c>
+      <c r="G25" s="14">
         <v>50</v>
       </c>
-      <c r="G25" s="14">
-        <v>52</v>
-      </c>
       <c r="H25" s="15">
-        <v>-3.846153846153</v>
+        <v>-4</v>
       </c>
       <c r="I25" s="14">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="J25" s="14">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.070707070707</v>
+        <v>-6.572769953051</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.615023474178</v>
+        <v>-8.294930875576</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D26" s="14">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E26" s="15">
-        <v>53.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="G26" s="14">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H26" s="15">
-        <v>37.373737373737</v>
+        <v>30.208333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="J26" s="14">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="K26" s="15">
-        <v>12.365591397849</v>
+        <v>11.616161616161</v>
       </c>
       <c r="L26" s="15">
-        <v>20.809248554913</v>
+        <v>17.866666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>39.333333333333</v>
+        <v>38.125</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
         <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J27" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>10.526315789473</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,72 +1426,72 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
       <c r="E28" s="15">
-        <v>-66.666666666666</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>10</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I28" s="14">
+        <v>40</v>
+      </c>
+      <c r="J28" s="14">
         <v>37</v>
       </c>
-      <c r="J28" s="14">
-        <v>36</v>
-      </c>
       <c r="K28" s="15">
-        <v>2.777777777777</v>
+        <v>8.108108108108</v>
       </c>
       <c r="L28" s="15">
-        <v>-13.953488372093</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E29" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-87.5</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
       </c>
       <c r="J29" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K29" s="15">
-        <v>-27.272727272727</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L29" s="15">
         <v>-33.333333333333</v>
@@ -1500,39 +1500,39 @@
         <v>-52.941176470588</v>
       </c>
       <c r="N29" s="15">
-        <v>-84.313725490196</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E30" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H30" s="15">
-        <v>-75</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I30" s="14">
         <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K30" s="15">
-        <v>-27.272727272727</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>-27.272727272727</v>
@@ -1541,7 +1541,7 @@
         <v>-27.272727272727</v>
       </c>
       <c r="N30" s="15">
-        <v>-81.818181818181</v>
+        <v>-83.673469387755</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,38 +1551,38 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>200</v>
       </c>
       <c r="L31" s="15">
         <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1638,10 +1638,10 @@
         <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>81</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2162</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1165</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1374</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>1206</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>1172</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>7232</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,6 +202,9 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
   </si>
   <si>
@@ -224,9 +227,6 @@
   </si>
   <si>
     <t>Transit</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>2</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
@@ -890,34 +890,34 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="14">
+        <v>22</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="G15" s="14">
-        <v>7</v>
-      </c>
       <c r="H15" s="15">
-        <v>-14.285714285714</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>18</v>
       </c>
       <c r="J15" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L15" s="15">
         <v>38.461538461538</v>
@@ -931,253 +931,253 @@
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14">
         <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E16" s="15">
-        <v>-42.857142857142</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F16" s="14">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G16" s="14">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="H16" s="15">
-        <v>2.272727272727</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I16" s="14">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="J16" s="14">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="K16" s="15">
-        <v>9.333333333333</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.344632768361</v>
+        <v>-11.794871794871</v>
       </c>
       <c r="M16" s="15">
-        <v>32.258064516129</v>
+        <v>21.985815602836</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.156196943972</v>
+        <v>-72.567783094098</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D17" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E17" s="15">
-        <v>-42.105263157894</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G17" s="14">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.710843373494</v>
+        <v>-8.108108108108</v>
       </c>
       <c r="I17" s="14">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="J17" s="14">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.347826086956</v>
+        <v>-2.077151335311</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>0.917431192660</v>
       </c>
       <c r="M17" s="15">
-        <v>161.016949152542</v>
+        <v>150</v>
       </c>
       <c r="N17" s="15">
-        <v>-3.144654088050</v>
+        <v>-2.654867256637</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>10</v>
+      </c>
+      <c r="D18" s="14">
         <v>5</v>
       </c>
-      <c r="D18" s="14">
-        <v>11</v>
-      </c>
       <c r="E18" s="15">
-        <v>-54.545454545454</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
         <v>30</v>
       </c>
       <c r="G18" s="14">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="I18" s="14">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="J18" s="14">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="K18" s="15">
-        <v>-25.185185185185</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-7.339449541284</v>
+        <v>-0.884955752212</v>
       </c>
       <c r="M18" s="15">
-        <v>68.333333333333</v>
+        <v>72.307692307692</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.066350710900</v>
+        <v>-75.330396475770</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14">
         <v>18</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E19" s="15">
-        <v>5.882352941176</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G19" s="14">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H19" s="15">
-        <v>-25.641025641025</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="I19" s="14">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="J19" s="14">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.225352112676</v>
+        <v>-4.262295081967</v>
       </c>
       <c r="L19" s="15">
-        <v>-6.529209621993</v>
+        <v>-7.006369426751</v>
       </c>
       <c r="M19" s="15">
-        <v>122.950819672131</v>
+        <v>131.746031746032</v>
       </c>
       <c r="N19" s="15">
-        <v>43.157894736842</v>
+        <v>39.712918660287</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-77.777777777777</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F20" s="14">
         <v>15</v>
       </c>
       <c r="G20" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H20" s="15">
-        <v>-44.444444444444</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J20" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.829268292682</v>
+        <v>-28.089887640449</v>
       </c>
       <c r="L20" s="15">
-        <v>-13.043478260869</v>
+        <v>-9.859154929577</v>
       </c>
       <c r="M20" s="15">
-        <v>93.548387096774</v>
+        <v>88.235294117647</v>
       </c>
       <c r="N20" s="15">
-        <v>-72.093023255813</v>
+        <v>-71.929824561403</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D21" s="17">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E21" s="18">
-        <v>-36.986301369863</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="F21" s="17">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="G21" s="17">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.382671480144</v>
+        <v>-21.223021582733</v>
       </c>
       <c r="I21" s="17">
-        <v>925</v>
+        <v>990</v>
       </c>
       <c r="J21" s="17">
-        <v>996</v>
+        <v>1064</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.128514056224</v>
+        <v>-6.954887218045</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.933196300102</v>
+        <v>-4.716073147256</v>
       </c>
       <c r="M21" s="18">
-        <v>99.353448275862</v>
+        <v>95.266272189349</v>
       </c>
       <c r="N21" s="18">
-        <v>-47.916666666666</v>
+        <v>-47.867298578199</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>20</v>
@@ -1189,31 +1189,31 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I22" s="14">
         <v>21</v>
       </c>
       <c r="J22" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K22" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>23.529411764705</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D23" s="14">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-58.823529411764</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G23" s="14">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H23" s="15">
-        <v>-43.396226415094</v>
+        <v>-27.083333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J23" s="14">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="K23" s="15">
-        <v>-13.253012048192</v>
+        <v>-6.395348837209</v>
       </c>
       <c r="L23" s="15">
-        <v>-9.433962264150</v>
+        <v>-4.733727810650</v>
       </c>
       <c r="M23" s="15">
-        <v>89.473684210526</v>
+        <v>82.954545454545</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D24" s="14">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E24" s="15">
-        <v>-6.451612903225</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="G24" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="H24" s="15">
-        <v>6.451612903225</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I24" s="14">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="J24" s="14">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="K24" s="15">
-        <v>1.308411214953</v>
+        <v>0.517241379310</v>
       </c>
       <c r="L24" s="15">
-        <v>4.230769230769</v>
+        <v>7.564575645756</v>
       </c>
       <c r="M24" s="15">
-        <v>44.533333333333</v>
+        <v>47.222222222222</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.666666666666</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H25" s="15">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="I25" s="14">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="J25" s="14">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="K25" s="15">
-        <v>-6.572769953051</v>
+        <v>-9.787234042553</v>
       </c>
       <c r="L25" s="15">
-        <v>-8.294930875576</v>
+        <v>-5.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D26" s="14">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G26" s="14">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" s="15">
-        <v>30.208333333333</v>
+        <v>36.082474226804</v>
       </c>
       <c r="I26" s="14">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="J26" s="14">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="K26" s="15">
-        <v>11.616161616161</v>
+        <v>13.875598086124</v>
       </c>
       <c r="L26" s="15">
-        <v>17.866666666666</v>
+        <v>21.119592875318</v>
       </c>
       <c r="M26" s="15">
-        <v>38.125</v>
+        <v>39.589442815249</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
         <v>6</v>
       </c>
       <c r="G27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I27" s="14">
+        <v>22</v>
+      </c>
+      <c r="J27" s="14">
+        <v>25</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-12</v>
+      </c>
+      <c r="L27" s="15">
+        <v>10</v>
+      </c>
+      <c r="M27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J27" s="14">
-        <v>23</v>
-      </c>
-      <c r="K27" s="15">
-        <v>-8.695652173913</v>
-      </c>
-      <c r="L27" s="15">
-        <v>10.526315789473</v>
-      </c>
-      <c r="M27" s="13" t="s">
-        <v>29</v>
-      </c>
       <c r="N27" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>7</v>
@@ -1444,22 +1444,22 @@
         <v>-30</v>
       </c>
       <c r="I28" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J28" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K28" s="15">
-        <v>8.108108108108</v>
+        <v>7.894736842105</v>
       </c>
       <c r="L28" s="15">
-        <v>-9.090909090909</v>
+        <v>-18</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,28 +1479,28 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H29" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
       </c>
       <c r="J29" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K29" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L29" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
-        <v>-52.941176470588</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1511,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" s="15">
         <v>-100</v>
@@ -1520,28 +1520,28 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H30" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I30" s="14">
         <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K30" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="15">
         <v>-27.272727272727</v>
       </c>
       <c r="M30" s="15">
-        <v>-27.272727272727</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N30" s="15">
-        <v>-83.673469387755</v>
+        <v>-84.615384615384</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1579,10 +1579,10 @@
         <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,41 +1607,41 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1</v>
+      </c>
+      <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="14">
         <v>2</v>
       </c>
       <c r="K33" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L33" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>81</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C41" s="14">
         <v>2162</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C42" s="14">
         <v>1165</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C43" s="14">
         <v>1374</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C44" s="14">
         <v>1206</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" s="14">
         <v>1172</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C46" s="17">
         <v>7232</v>

--- a/data/source/weekly/cs-en-us-040pct.xlsx
+++ b/data/source/weekly/cs-en-us-040pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -202,31 +202,31 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
+    <t>Robbery</t>
+  </si>
+  <si>
+    <t>Fel. Assault</t>
+  </si>
+  <si>
+    <t>Burglary</t>
+  </si>
+  <si>
+    <t>Gr. Larceny</t>
+  </si>
+  <si>
+    <t>G.L.A.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
-  </si>
-  <si>
-    <t>Robbery</t>
-  </si>
-  <si>
-    <t>Fel. Assault</t>
-  </si>
-  <si>
-    <t>Burglary</t>
-  </si>
-  <si>
-    <t>Gr. Larceny</t>
-  </si>
-  <si>
-    <t>G.L.A.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Transit</t>
   </si>
   <si>
     <t>Housing</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="14">
         <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I14" s="14">
         <v>2</v>
       </c>
       <c r="J14" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K14" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L14" s="15">
         <v>-66.666666666666</v>
@@ -885,335 +885,335 @@
         <v>-33.333333333333</v>
       </c>
       <c r="N14" s="15">
-        <v>-91.304347826087</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
+        <v>7</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="15">
+        <v>40</v>
+      </c>
+      <c r="I15" s="14">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>5</v>
-      </c>
-      <c r="G15" s="14">
-        <v>6</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-16.666666666666</v>
-      </c>
-      <c r="I15" s="14">
-        <v>18</v>
-      </c>
       <c r="J15" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K15" s="15">
-        <v>-10</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L15" s="15">
-        <v>38.461538461538</v>
+        <v>37.5</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>266.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-5.263157894736</v>
+        <v>4.761904761904</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" s="14">
         <v>18</v>
       </c>
       <c r="E16" s="15">
-        <v>-55.555555555555</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="F16" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="H16" s="15">
-        <v>-27.777777777777</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I16" s="14">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J16" s="14">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="K16" s="15">
-        <v>2.380952380952</v>
+        <v>-1.612903225806</v>
       </c>
       <c r="L16" s="15">
-        <v>-11.794871794871</v>
+        <v>-12.440191387559</v>
       </c>
       <c r="M16" s="15">
-        <v>21.985815602836</v>
+        <v>23.648648648648</v>
       </c>
       <c r="N16" s="15">
-        <v>-72.567783094098</v>
+        <v>-72.522522522522</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>11.764705882352</v>
       </c>
       <c r="F17" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="G17" s="14">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.108108108108</v>
+        <v>9.722222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>330</v>
+        <v>353</v>
       </c>
       <c r="J17" s="14">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.077151335311</v>
+        <v>-0.282485875706</v>
       </c>
       <c r="L17" s="15">
-        <v>0.917431192660</v>
+        <v>2.023121387283</v>
       </c>
       <c r="M17" s="15">
-        <v>150</v>
+        <v>138.513513513514</v>
       </c>
       <c r="N17" s="15">
-        <v>-2.654867256637</v>
+        <v>-3.021978021978</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="14">
+        <v>4</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F18" s="14">
+        <v>24</v>
+      </c>
+      <c r="G18" s="14">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>10</v>
-      </c>
-      <c r="D18" s="14">
-        <v>5</v>
-      </c>
-      <c r="E18" s="15">
-        <v>100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>30</v>
-      </c>
-      <c r="G18" s="14">
-        <v>32</v>
-      </c>
       <c r="H18" s="15">
-        <v>-6.25</v>
+        <v>-4</v>
       </c>
       <c r="I18" s="14">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J18" s="14">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-0.884955752212</v>
+        <v>-3.305785123966</v>
       </c>
       <c r="M18" s="15">
-        <v>72.307692307692</v>
+        <v>67.142857142857</v>
       </c>
       <c r="N18" s="15">
-        <v>-75.330396475770</v>
+        <v>-75.675675675675</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D19" s="14">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F19" s="14">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="G19" s="14">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H19" s="15">
-        <v>-24.691358024691</v>
+        <v>4.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="J19" s="14">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="K19" s="15">
-        <v>-4.262295081967</v>
+        <v>-1.567398119122</v>
       </c>
       <c r="L19" s="15">
-        <v>-7.006369426751</v>
+        <v>-5.705705705705</v>
       </c>
       <c r="M19" s="15">
-        <v>131.746031746032</v>
+        <v>134.328358208955</v>
       </c>
       <c r="N19" s="15">
-        <v>39.712918660287</v>
+        <v>35.930735930735</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E20" s="15">
-        <v>-42.857142857142</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H20" s="15">
-        <v>-48.275862068965</v>
+        <v>-46.875</v>
       </c>
       <c r="I20" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="J20" s="14">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K20" s="15">
-        <v>-28.089887640449</v>
+        <v>-27.835051546391</v>
       </c>
       <c r="L20" s="15">
-        <v>-9.859154929577</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="M20" s="15">
-        <v>88.235294117647</v>
+        <v>79.487179487179</v>
       </c>
       <c r="N20" s="15">
-        <v>-71.929824561403</v>
+        <v>-71.074380165289</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="17">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E21" s="18">
-        <v>-10.294117647058</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="G21" s="17">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.223021582733</v>
+        <v>-10.408921933085</v>
       </c>
       <c r="I21" s="17">
-        <v>990</v>
+        <v>1061</v>
       </c>
       <c r="J21" s="17">
-        <v>1064</v>
+        <v>1126</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.954887218045</v>
+        <v>-5.772646536412</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.716073147256</v>
+        <v>-3.981900452488</v>
       </c>
       <c r="M21" s="18">
-        <v>95.266272189349</v>
+        <v>93.613138686131</v>
       </c>
       <c r="N21" s="18">
-        <v>-47.867298578199</v>
+        <v>-47.759724273756</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="15">
-        <v>-85.714285714285</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" s="14">
         <v>28</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L22" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M22" s="15">
-        <v>23.529411764705</v>
+        <v>4.761904761904</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E23" s="15">
-        <v>133.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="F23" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G23" s="14">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.083333333333</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="I23" s="14">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="J23" s="14">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K23" s="15">
-        <v>-6.395348837209</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L23" s="15">
-        <v>-4.733727810650</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M23" s="15">
-        <v>82.954545454545</v>
+        <v>73.469387755102</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D24" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E24" s="15">
-        <v>-11.111111111111</v>
+        <v>-37.209302325581</v>
       </c>
       <c r="F24" s="14">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G24" s="14">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="H24" s="15">
-        <v>3.703703703703</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="J24" s="14">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="K24" s="15">
-        <v>0.517241379310</v>
+        <v>-2.407704654895</v>
       </c>
       <c r="L24" s="15">
-        <v>7.564575645756</v>
+        <v>3.225806451612</v>
       </c>
       <c r="M24" s="15">
-        <v>47.222222222222</v>
+        <v>43.735224586288</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-40.909090909090</v>
+        <v>-37.5</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H25" s="15">
-        <v>-15</v>
+        <v>-19.298245614035</v>
       </c>
       <c r="I25" s="14">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="J25" s="14">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="K25" s="15">
-        <v>-9.787234042553</v>
+        <v>-10.756972111553</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.777777777777</v>
+        <v>-7.053941908713</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D26" s="14">
         <v>22</v>
       </c>
       <c r="E26" s="15">
-        <v>54.545454545454</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G26" s="14">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H26" s="15">
-        <v>36.082474226804</v>
+        <v>27.083333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="J26" s="14">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="K26" s="15">
-        <v>13.875598086124</v>
+        <v>12.5</v>
       </c>
       <c r="L26" s="15">
-        <v>21.119592875318</v>
+        <v>17.021276595744</v>
       </c>
       <c r="M26" s="15">
-        <v>39.589442815249</v>
+        <v>31.299734748010</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,40 +1385,40 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
       <c r="E27" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F27" s="14">
+        <v>8</v>
+      </c>
+      <c r="G27" s="14">
         <v>6</v>
       </c>
-      <c r="G27" s="14">
-        <v>8</v>
-      </c>
       <c r="H27" s="15">
-        <v>-25</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J27" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K27" s="15">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>10</v>
+        <v>13.043478260869</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1426,40 +1426,40 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H28" s="15">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>41</v>
       </c>
       <c r="J28" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K28" s="15">
-        <v>7.894736842105</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-18</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,28 +1479,28 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H29" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.909090909090</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
       </c>
       <c r="J29" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K29" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M29" s="15">
-        <v>-61.904761904761</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.666666666666</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1520,69 +1520,69 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H30" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="I30" s="14">
         <v>8</v>
       </c>
       <c r="J30" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="L30" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="15">
-        <v>-42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N30" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>1</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="14">
         <v>1</v>
       </c>
       <c r="K31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1607,14 +1607,14 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="F33" s="14">
         <v>1</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I33" s="14">
         <v>2</v>
@@ -1638,10 +1638,10 @@
         <v>100</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>81</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="41" spans="1:14">
       <c r="A41" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C41" s="14">
         <v>2162</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C42" s="14">
         <v>1165</v>
@@ -1868,7 +1868,7 @@
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C43" s="14">
         <v>1374</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C44" s="14">
         <v>1206</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C45" s="14">
         <v>1172</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="17">
         <v>7232</v>
